--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_20_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_20_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M2" t="n">
         <v>10</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>10</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>23</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X17" t="n">
         <v>7</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X18" t="n">
         <v>6</v>
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>3</v>
@@ -2119,10 +2119,10 @@
         <v>9</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2511,16 +2511,16 @@
         <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>2</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>100</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X30" t="n">
         <v>30</v>
@@ -4684,16 +4684,16 @@
         <v>38</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X37" t="n">
         <v>7</v>
@@ -5076,16 +5076,16 @@
         <v>8</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
         <v>5</v>
@@ -5664,16 +5664,16 @@
         <v>2</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" t="n">
         <v>3</v>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6056,7 +6056,7 @@
         <v>19</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>90</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
         <v>26</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_20_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_20_EL.xlsx
@@ -674,10 +674,10 @@
         <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="O2" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -692,20 +692,20 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O3" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="P3" t="n">
         <v>7</v>
@@ -854,17 +854,17 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
         <v>6</v>
       </c>
       <c r="W3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>3</v>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -1543,14 +1543,14 @@
         <v>3</v>
       </c>
       <c r="X18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y18" t="n">
         <v>6</v>
       </c>
-      <c r="Y18" t="n">
-        <v>9</v>
-      </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -2131,14 +2131,14 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA21" t="n">
@@ -2327,14 +2327,14 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2719,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3144,25 +3144,25 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -3503,14 +3503,14 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>8</v>
       </c>
       <c r="X30" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="Y30" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4696,14 +4696,14 @@
         <v>2</v>
       </c>
       <c r="X37" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y37" t="n">
         <v>7</v>
       </c>
-      <c r="Y37" t="n">
-        <v>10</v>
-      </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -5088,14 +5088,14 @@
         <v>1</v>
       </c>
       <c r="X39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y39" t="n">
         <v>5</v>
       </c>
-      <c r="Y39" t="n">
-        <v>7</v>
-      </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5124,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
@@ -6460,14 +6460,14 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6796,14 +6796,14 @@
         <v>4</v>
       </c>
       <c r="X48" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Y48" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6832,7 +6832,7 @@
         <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
@@ -6843,11 +6843,11 @@
         <v>6</v>
       </c>
       <c r="AK48" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
